--- a/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DD9EF2FF-488E-4B71-B428-19C8C492E256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF52C1A7-6AB6-4EBB-8BD2-E0AE2EAC52F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2215" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2679" uniqueCount="208">
   <si>
     <t>C1</t>
   </si>
@@ -579,13 +579,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S3aH3,S1aH3,S2aH2,S3aH2,S1aH2,S2aH3</t>
+    <t>S1aH3,S1aH2,S2aH3,S2aH2,S3aH2,S3aH3</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S1aH4,S2aH1,S1aH1,S3aH4,S1aH5,S2aH4,S2aH5,S3aH1,S3aH5</t>
+    <t>S1aH1,S3aH4,S3aH1,S3aH5,S2aH1,S1aH5,S2aH4,S2aH5,S1aH4</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -595,6 +595,9 @@
   </si>
   <si>
     <t>pset_ci</t>
+  </si>
+  <si>
+    <t>hydro</t>
   </si>
   <si>
     <t>AllS</t>
@@ -660,10 +663,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,FaD,WaD,RaD,WaP,SaD,RaP</t>
+    <t>SaD,FaP,SaP,RaD,FaD,RaP,WaD,WaP</t>
   </si>
   <si>
-    <t>RaP,RaN,FaP,SaP,FaN,WaP,SaN,WaN</t>
+    <t>FaP,SaP,SaN,WaN,FaN,RaP,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -23441,13 +23444,13 @@
         <v>177</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I11" t="s">
         <v>177</v>
       </c>
       <c r="J11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
@@ -23462,13 +23465,13 @@
         <v>179</v>
       </c>
       <c r="G12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I12" t="s">
         <v>179</v>
       </c>
       <c r="J12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="3:13" x14ac:dyDescent="0.45">
@@ -23587,8 +23590,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E5137E-1939-4159-BFC6-E4175E83B6F7}">
-  <dimension ref="A9:AN40"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E86F13C5-91B8-4765-B22A-FB3892CE9C7F}">
+  <dimension ref="A9:AN97"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -23809,6 +23812,18 @@
       <c r="AI11">
         <v>0.19756037558773065</v>
       </c>
+      <c r="AK11">
+        <v>2020</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM11">
+        <v>0.46683481569980972</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
@@ -23886,6 +23901,18 @@
       <c r="AI12">
         <v>5.3223687573688006E-2</v>
       </c>
+      <c r="AK12">
+        <v>2020</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM12">
+        <v>0.5001238484258026</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
@@ -23963,6 +23990,18 @@
       <c r="AI13">
         <v>0.22197418450607564</v>
       </c>
+      <c r="AK13">
+        <v>2020</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM13">
+        <v>0.3986997676615211</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E14" t="s">
@@ -24037,6 +24076,18 @@
       <c r="AI14">
         <v>0.1513823981439868</v>
       </c>
+      <c r="AK14">
+        <v>2021</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM14">
+        <v>0.4216692305727629</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.45">
       <c r="E15" t="s">
@@ -24111,6 +24162,18 @@
       <c r="AI15">
         <v>0.12100710982770413</v>
       </c>
+      <c r="AK15">
+        <v>2021</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM15">
+        <v>0.48848366565878643</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.45">
       <c r="I16" t="s">
@@ -24179,8 +24242,20 @@
       <c r="AI16">
         <v>0.17448571917839417</v>
       </c>
-    </row>
-    <row r="17" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2021</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM16">
+        <v>0.3636038703594191</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I17" t="s">
         <v>156</v>
       </c>
@@ -24247,8 +24322,20 @@
       <c r="AI17">
         <v>6.0537117070712299E-2</v>
       </c>
-    </row>
-    <row r="18" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2022</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM17">
+        <v>0.47973343518028871</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I18" t="s">
         <v>156</v>
       </c>
@@ -24315,8 +24402,20 @@
       <c r="AI18">
         <v>0.25851050443010148</v>
       </c>
-    </row>
-    <row r="19" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2022</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM18">
+        <v>0.52256896353934956</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I19" t="s">
         <v>156</v>
       </c>
@@ -24383,8 +24482,20 @@
       <c r="AI19">
         <v>0.15855700420216179</v>
       </c>
-    </row>
-    <row r="20" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2022</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM19">
+        <v>0.43824929871407342</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I20" t="s">
         <v>156</v>
       </c>
@@ -24451,8 +24562,20 @@
       <c r="AI20">
         <v>0.18303171271170715</v>
       </c>
-    </row>
-    <row r="21" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2025</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM20">
+        <v>0.42680000000000001</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I21" t="s">
         <v>156</v>
       </c>
@@ -24519,8 +24642,20 @@
       <c r="AI21">
         <v>0.26493020206716933</v>
       </c>
-    </row>
-    <row r="22" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2025</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM21">
+        <v>0.43864999999999998</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I22" t="s">
         <v>156</v>
       </c>
@@ -24587,8 +24722,20 @@
       <c r="AI22">
         <v>0.12516007959314202</v>
       </c>
-    </row>
-    <row r="23" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2025</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM22">
+        <v>0.35719999999999996</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I23" t="s">
         <v>156</v>
       </c>
@@ -24655,8 +24802,20 @@
       <c r="AI23">
         <v>0.35173530360483118</v>
       </c>
-    </row>
-    <row r="24" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2026</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM23">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I24" t="s">
         <v>156</v>
       </c>
@@ -24723,8 +24882,20 @@
       <c r="AI24">
         <v>0.27787886784651428</v>
       </c>
-    </row>
-    <row r="25" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2026</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM24">
+        <v>0.45679999999999998</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I25" t="s">
         <v>156</v>
       </c>
@@ -24791,8 +24962,20 @@
       <c r="AI25">
         <v>0.23840129943405119</v>
       </c>
-    </row>
-    <row r="26" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2026</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM25">
+        <v>0.34400000000000003</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC26" t="s">
         <v>19</v>
       </c>
@@ -24802,8 +24985,20 @@
       <c r="AE26">
         <v>2.4625517249733362E-2</v>
       </c>
-    </row>
-    <row r="27" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2027</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM26">
+        <v>0.38690000000000002</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC27" t="s">
         <v>19</v>
       </c>
@@ -24813,8 +25008,20 @@
       <c r="AE27">
         <v>3.492321304493205E-3</v>
       </c>
-    </row>
-    <row r="28" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2027</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM27">
+        <v>0.43074999999999997</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC28" t="s">
         <v>19</v>
       </c>
@@ -24824,8 +25031,20 @@
       <c r="AE28">
         <v>3.544990298376148E-2</v>
       </c>
-    </row>
-    <row r="29" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2027</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM28">
+        <v>0.35739999999999994</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC29" t="s">
         <v>19</v>
       </c>
@@ -24835,8 +25054,20 @@
       <c r="AE29">
         <v>3.5654564848759712E-3</v>
       </c>
-    </row>
-    <row r="30" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2028</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM29">
+        <v>0.51029999999999998</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC30" t="s">
         <v>19</v>
       </c>
@@ -24846,8 +25077,20 @@
       <c r="AE30">
         <v>1.7824978853751637E-2</v>
       </c>
-    </row>
-    <row r="31" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2028</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM30">
+        <v>0.53774999999999995</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC31" t="s">
         <v>19</v>
       </c>
@@ -24857,8 +25100,20 @@
       <c r="AE31">
         <v>4.6933445656837082E-2</v>
       </c>
-    </row>
-    <row r="32" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2028</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM31">
+        <v>0.4604111111111111</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC32" t="s">
         <v>19</v>
       </c>
@@ -24868,8 +25123,20 @@
       <c r="AE32">
         <v>6.6346099310041814E-3</v>
       </c>
-    </row>
-    <row r="33" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2029</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM32">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC33" t="s">
         <v>19</v>
       </c>
@@ -24879,8 +25146,20 @@
       <c r="AE33">
         <v>6.7416826726653195E-2</v>
       </c>
-    </row>
-    <row r="34" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2029</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM33">
+        <v>0.57820000000000005</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC34" t="s">
         <v>19</v>
       </c>
@@ -24890,8 +25169,20 @@
       <c r="AE34">
         <v>6.8028560902962465E-3</v>
       </c>
-    </row>
-    <row r="35" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK34">
+        <v>2029</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM34">
+        <v>0.46450000000000002</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC35" t="s">
         <v>19</v>
       </c>
@@ -24901,8 +25192,20 @@
       <c r="AE35">
         <v>3.3933483313697284E-2</v>
       </c>
-    </row>
-    <row r="36" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2030</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM35">
+        <v>0.59360000000000002</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC36" t="s">
         <v>19</v>
       </c>
@@ -24912,8 +25215,20 @@
       <c r="AE36">
         <v>0.2185574580193263</v>
       </c>
-    </row>
-    <row r="37" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2030</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM36">
+        <v>0.55840000000000001</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC37" t="s">
         <v>19</v>
       </c>
@@ -24923,8 +25238,20 @@
       <c r="AE37">
         <v>3.0936151562624165E-2</v>
       </c>
-    </row>
-    <row r="38" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2030</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM37">
+        <v>0.49422222222222228</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC38" t="s">
         <v>19</v>
       </c>
@@ -24934,8 +25261,20 @@
       <c r="AE38">
         <v>0.31398842749103195</v>
       </c>
-    </row>
-    <row r="39" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2031</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM38">
+        <v>0.57379999999999998</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC39" t="s">
         <v>19</v>
       </c>
@@ -24945,8 +25284,20 @@
       <c r="AE39">
         <v>3.1563748814684989E-2</v>
       </c>
-    </row>
-    <row r="40" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2031</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM39">
+        <v>0.60430000000000006</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC40" t="s">
         <v>19</v>
       </c>
@@ -24955,6 +25306,816 @@
       </c>
       <c r="AE40">
         <v>0.15827481551722897</v>
+      </c>
+      <c r="AK40">
+        <v>2031</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM40">
+        <v>0.47028888888888887</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2032</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM41">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2032</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM42">
+        <v>0.55594999999999994</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2032</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM43">
+        <v>0.4785666666666667</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2033</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM44">
+        <v>0.50170000000000003</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2033</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM45">
+        <v>0.62080000000000002</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2033</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM46">
+        <v>0.47124444444444435</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2034</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM47">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2034</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM48">
+        <v>0.59325000000000006</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2034</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM49">
+        <v>0.47331111111111113</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2035</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM50">
+        <v>0.56969999999999998</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2035</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM51">
+        <v>0.59604999999999997</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2035</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM52">
+        <v>0.49247777777777774</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2036</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM53">
+        <v>0.48930000000000001</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2036</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM54">
+        <v>0.51669999999999994</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2036</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM55">
+        <v>0.41644444444444445</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2037</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM56">
+        <v>0.4466</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2037</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM57">
+        <v>0.50214999999999999</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2037</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM58">
+        <v>0.40861111111111115</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2038</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM59">
+        <v>0.51359999999999995</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2038</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM60">
+        <v>0.51405000000000001</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2038</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM61">
+        <v>0.40710000000000002</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2039</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM62">
+        <v>0.45850000000000002</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2039</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM63">
+        <v>0.502</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2039</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM64">
+        <v>0.40135555555555563</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2040</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM65">
+        <v>0.44779999999999998</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2040</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM66">
+        <v>0.51239999999999997</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2040</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM67">
+        <v>0.41443333333333338</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2041</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM68">
+        <v>0.43390000000000001</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2041</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM69">
+        <v>0.48904999999999998</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2041</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM70">
+        <v>0.40888888888888886</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2042</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM71">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2042</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM72">
+        <v>0.52539999999999998</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2042</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM73">
+        <v>0.39182222222222218</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2043</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM74">
+        <v>0.51939999999999997</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2043</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM75">
+        <v>0.50159999999999993</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2043</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM76">
+        <v>0.40468888888888888</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2044</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM77">
+        <v>0.45629999999999998</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2044</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM78">
+        <v>0.50209999999999999</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2044</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM79">
+        <v>0.40970000000000001</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2045</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM80">
+        <v>0.48280000000000001</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2045</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM81">
+        <v>0.47384999999999999</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2045</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM82">
+        <v>0.3958888888888889</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2046</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM83">
+        <v>0.44540000000000002</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2046</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM84">
+        <v>0.50385000000000002</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2046</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM85">
+        <v>0.40318888888888887</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2047</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM86">
+        <v>0.51580000000000004</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2047</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM87">
+        <v>0.46450000000000002</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2047</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM88">
+        <v>0.40820000000000001</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK89">
+        <v>2048</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM89">
+        <v>0.4788</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="90" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK90">
+        <v>2048</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM90">
+        <v>0.4622</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK91">
+        <v>2048</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM91">
+        <v>0.40722222222222221</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK92">
+        <v>2049</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM92">
+        <v>0.40860000000000002</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK93">
+        <v>2049</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM93">
+        <v>0.44564999999999999</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK94">
+        <v>2049</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM94">
+        <v>0.33861111111111114</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK95">
+        <v>2050</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM95">
+        <v>0.3639</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK96">
+        <v>2050</v>
+      </c>
+      <c r="AL96" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM96">
+        <v>0.41885</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="97" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK97">
+        <v>2050</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM97">
+        <v>0.3448222222222222</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -24963,8 +26124,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D8B90A5-4F50-4FD1-9192-072F140E7D8A}">
-  <dimension ref="A9:AN12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6523DE93-28B1-40DF-B5CA-72803F975C3A}">
+  <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -25105,16 +26266,16 @@
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
       </c>
       <c r="E11" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" t="s">
         <v>185</v>
-      </c>
-      <c r="F11" t="s">
-        <v>184</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -25123,7 +26284,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K11">
         <v>0.99999999999979605</v>
@@ -25135,7 +26296,7 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P11">
         <v>0.99999999999975986</v>
@@ -25147,7 +26308,7 @@
         <v>174</v>
       </c>
       <c r="T11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="U11">
         <v>0.99999999999977052</v>
@@ -25162,7 +26323,7 @@
         <v>1.0000000000000002</v>
       </c>
       <c r="Z11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -25171,7 +26332,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AE11">
         <v>1</v>
@@ -25180,10 +26341,22 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AI11">
         <v>0.33758082105685405</v>
+      </c>
+      <c r="AK11">
+        <v>2020</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM11">
+        <v>0.42128170179209201</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
@@ -25191,10 +26364,400 @@
         <v>19</v>
       </c>
       <c r="AD12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AE12">
         <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>2021</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM12">
+        <v>0.38925594959375892</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK13">
+        <v>2022</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM13">
+        <v>0.45575958755713736</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK14">
+        <v>2025</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM14">
+        <v>0.37657500000000005</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK15">
+        <v>2026</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM15">
+        <v>0.36588333333333334</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2027</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM16">
+        <v>0.37208333333333332</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2028</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM17">
+        <v>0.47745833333333326</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2029</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM18">
+        <v>0.49290833333333328</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2030</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM19">
+        <v>0.51319999999999999</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2031</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM20">
+        <v>0.50124999999999997</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2032</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM21">
+        <v>0.4941666666666667</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2033</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM22">
+        <v>0.49870833333333331</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2034</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM23">
+        <v>0.50119166666666659</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2035</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM24">
+        <v>0.51617500000000005</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2036</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM25">
+        <v>0.43922499999999998</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2037</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM26">
+        <v>0.42736666666666667</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2038</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM27">
+        <v>0.43379999999999996</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2039</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM28">
+        <v>0.42289166666666672</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2040</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM29">
+        <v>0.43354166666666666</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2041</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM30">
+        <v>0.4243333333333334</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2042</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM31">
+        <v>0.41860000000000003</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2043</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM32">
+        <v>0.43039999999999995</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2044</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM33">
+        <v>0.42898333333333333</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK34">
+        <v>2045</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM34">
+        <v>0.41612499999999991</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2046</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM35">
+        <v>0.42348333333333338</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2047</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM36">
+        <v>0.42655000000000004</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2048</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM37">
+        <v>0.42234999999999995</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2049</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM38">
+        <v>0.36228333333333329</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2050</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>185</v>
+      </c>
+      <c r="AM39">
+        <v>0.35874999999999996</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -25203,8 +26766,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F61B8EE0-E1B4-46A5-BEF7-A268CE6E5A22}">
-  <dimension ref="A9:AN34"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9991FA3A-A973-4064-836C-52C99158196F}">
+  <dimension ref="A9:AN126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="1:40" x14ac:dyDescent="0.45">
@@ -25345,7 +26908,7 @@
         <v>x</v>
       </c>
       <c r="C11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
         <v>146</v>
@@ -25354,7 +26917,7 @@
         <v>177</v>
       </c>
       <c r="F11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G11" t="s">
         <v>146</v>
@@ -25363,7 +26926,7 @@
         <v>156</v>
       </c>
       <c r="J11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K11">
         <v>0.25600060352273007</v>
@@ -25375,7 +26938,7 @@
         <v>173</v>
       </c>
       <c r="O11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P11">
         <v>0.12378336272189555</v>
@@ -25387,7 +26950,7 @@
         <v>174</v>
       </c>
       <c r="T11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U11">
         <v>0.13703067684622752</v>
@@ -25402,7 +26965,7 @@
         <v>0.16087081189037786</v>
       </c>
       <c r="Z11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA11" t="s">
         <v>25</v>
@@ -25411,7 +26974,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AE11">
         <v>0.10746750608365477</v>
@@ -25420,15 +26983,27 @@
         <v>97</v>
       </c>
       <c r="AH11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AI11">
         <v>0.28114388397789059</v>
       </c>
+      <c r="AK11">
+        <v>2020</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM11">
+        <v>0.40428015224097641</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E12" t="s">
         <v>179</v>
@@ -25440,7 +27015,7 @@
         <v>156</v>
       </c>
       <c r="J12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -25452,7 +27027,7 @@
         <v>173</v>
       </c>
       <c r="O12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P12">
         <v>0.16619871707167755</v>
@@ -25464,7 +27039,7 @@
         <v>174</v>
       </c>
       <c r="T12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="U12">
         <v>0.14426096308403169</v>
@@ -25479,7 +27054,7 @@
         <v>5.2547713165767528E-2</v>
       </c>
       <c r="Z12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA12" t="s">
         <v>25</v>
@@ -25488,7 +27063,7 @@
         <v>22</v>
       </c>
       <c r="AD12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE12">
         <v>0.11507795871804664</v>
@@ -25497,18 +27072,30 @@
         <v>97</v>
       </c>
       <c r="AH12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AI12">
         <v>0.24165119214111841</v>
       </c>
+      <c r="AK12">
+        <v>2020</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM12">
+        <v>0.43145550524195597</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G13" t="s">
         <v>146</v>
@@ -25517,7 +27104,7 @@
         <v>156</v>
       </c>
       <c r="J13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K13">
         <v>2.4662538277558481E-2</v>
@@ -25529,7 +27116,7 @@
         <v>173</v>
       </c>
       <c r="O13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P13">
         <v>2.3576706049808167E-2</v>
@@ -25541,7 +27128,7 @@
         <v>174</v>
       </c>
       <c r="T13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U13">
         <v>2.6155360437461635E-2</v>
@@ -25556,7 +27143,7 @@
         <v>3.5896543437005365E-2</v>
       </c>
       <c r="Z13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA13" t="s">
         <v>25</v>
@@ -25565,7 +27152,7 @@
         <v>22</v>
       </c>
       <c r="AD13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AE13">
         <v>2.2296812535938335E-2</v>
@@ -25574,21 +27161,33 @@
         <v>97</v>
       </c>
       <c r="AH13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AI13">
         <v>0.18224025353450046</v>
       </c>
+      <c r="AK13">
+        <v>2020</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM13">
+        <v>0.39318220679490351</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.45">
       <c r="C14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I14" t="s">
         <v>156</v>
       </c>
       <c r="J14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K14">
         <v>0.21353961933931231</v>
@@ -25600,7 +27199,7 @@
         <v>173</v>
       </c>
       <c r="O14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P14">
         <v>8.3470183732030565E-2</v>
@@ -25612,7 +27211,7 @@
         <v>174</v>
       </c>
       <c r="T14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U14">
         <v>9.9525775459301649E-2</v>
@@ -25627,7 +27226,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA14" t="s">
         <v>25</v>
@@ -25636,7 +27235,7 @@
         <v>22</v>
       </c>
       <c r="AD14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AE14">
         <v>0.10854061634593581</v>
@@ -25645,10 +27244,22 @@
         <v>97</v>
       </c>
       <c r="AH14" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AI14">
         <v>0.33254809651703798</v>
+      </c>
+      <c r="AK14">
+        <v>2020</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM14">
+        <v>0.45620894289053232</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.45">
@@ -25656,7 +27267,7 @@
         <v>156</v>
       </c>
       <c r="J15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K15">
         <v>1.1246142992547061E-6</v>
@@ -25668,7 +27279,7 @@
         <v>173</v>
       </c>
       <c r="O15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P15">
         <v>0.10894225880232646</v>
@@ -25680,7 +27291,7 @@
         <v>174</v>
       </c>
       <c r="T15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U15">
         <v>0.10953724700415568</v>
@@ -25695,7 +27306,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AA15" t="s">
         <v>25</v>
@@ -25704,7 +27315,7 @@
         <v>22</v>
       </c>
       <c r="AD15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AE15">
         <v>0.11880032319592665</v>
@@ -25713,10 +27324,22 @@
         <v>97</v>
       </c>
       <c r="AH15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AI15">
         <v>0.26427979361696696</v>
+      </c>
+      <c r="AK15">
+        <v>2021</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM15">
+        <v>0.33926186136744718</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.45">
@@ -25724,7 +27347,7 @@
         <v>156</v>
       </c>
       <c r="J16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K16">
         <v>2.2983337489004961E-2</v>
@@ -25736,7 +27359,7 @@
         <v>173</v>
       </c>
       <c r="O16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P16">
         <v>1.5584114069178085E-2</v>
@@ -25748,7 +27371,7 @@
         <v>174</v>
       </c>
       <c r="T16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U16">
         <v>2.0061972066498349E-2</v>
@@ -25763,7 +27386,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA16" t="s">
         <v>25</v>
@@ -25772,7 +27395,7 @@
         <v>22</v>
       </c>
       <c r="AD16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AE16">
         <v>2.3012000550329811E-2</v>
@@ -25781,18 +27404,30 @@
         <v>97</v>
       </c>
       <c r="AH16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AI16">
         <v>0.21652355545675173</v>
       </c>
-    </row>
-    <row r="17" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK16">
+        <v>2021</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM16">
+        <v>0.45440433006519898</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I17" t="s">
         <v>156</v>
       </c>
       <c r="J17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K17">
         <v>0.20641241133938554</v>
@@ -25804,7 +27439,7 @@
         <v>173</v>
       </c>
       <c r="O17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P17">
         <v>0.12207277062693601</v>
@@ -25816,7 +27451,7 @@
         <v>174</v>
       </c>
       <c r="T17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U17">
         <v>0.10788508198635595</v>
@@ -25831,7 +27466,7 @@
         <v>0.16263862301005233</v>
       </c>
       <c r="Z17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA17" t="s">
         <v>25</v>
@@ -25840,7 +27475,7 @@
         <v>22</v>
       </c>
       <c r="AD17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE17">
         <v>0.10299117185837108</v>
@@ -25849,18 +27484,30 @@
         <v>97</v>
       </c>
       <c r="AH17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AI17">
         <v>0.16699612170250089</v>
       </c>
-    </row>
-    <row r="18" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK17">
+        <v>2021</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM17">
+        <v>0.32268624665758983</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I18" t="s">
         <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -25872,7 +27519,7 @@
         <v>173</v>
       </c>
       <c r="O18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P18">
         <v>0.14318393959919393</v>
@@ -25884,7 +27531,7 @@
         <v>174</v>
       </c>
       <c r="T18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U18">
         <v>0.12028772921818569</v>
@@ -25899,7 +27546,7 @@
         <v>5.3125160563193538E-2</v>
       </c>
       <c r="Z18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA18" t="s">
         <v>25</v>
@@ -25908,7 +27555,7 @@
         <v>22</v>
       </c>
       <c r="AD18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE18">
         <v>0.11328122130945671</v>
@@ -25917,18 +27564,30 @@
         <v>97</v>
       </c>
       <c r="AH18" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AI18">
         <v>0.15429118361973715</v>
       </c>
-    </row>
-    <row r="19" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK18">
+        <v>2021</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM18">
+        <v>0.44067136028479997</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I19" t="s">
         <v>156</v>
       </c>
       <c r="J19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K19">
         <v>2.2147620465851774E-2</v>
@@ -25940,7 +27599,7 @@
         <v>173</v>
       </c>
       <c r="O19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P19">
         <v>2.1994357695343403E-2</v>
@@ -25952,7 +27611,7 @@
         <v>174</v>
       </c>
       <c r="T19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U19">
         <v>2.0688213681586812E-2</v>
@@ -25967,7 +27626,7 @@
         <v>3.6291010947302131E-2</v>
       </c>
       <c r="Z19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AA19" t="s">
         <v>25</v>
@@ -25976,7 +27635,7 @@
         <v>22</v>
       </c>
       <c r="AD19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE19">
         <v>2.1139518025726198E-2</v>
@@ -25985,18 +27644,30 @@
         <v>97</v>
       </c>
       <c r="AH19" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AI19">
         <v>8.5884208074758606E-2</v>
       </c>
-    </row>
-    <row r="20" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK19">
+        <v>2022</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM19">
+        <v>0.42231667003980294</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I20" t="s">
         <v>156</v>
       </c>
       <c r="J20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K20">
         <v>0.22684827956006251</v>
@@ -26008,7 +27679,7 @@
         <v>173</v>
       </c>
       <c r="O20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P20">
         <v>6.8819237727189592E-2</v>
@@ -26020,7 +27691,7 @@
         <v>174</v>
       </c>
       <c r="T20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U20">
         <v>8.9418967810014974E-2</v>
@@ -26035,7 +27706,7 @@
         <v>0.15910300077070333</v>
       </c>
       <c r="Z20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA20" t="s">
         <v>25</v>
@@ -26044,7 +27715,7 @@
         <v>22</v>
       </c>
       <c r="AD20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AE20">
         <v>0.11841310460254856</v>
@@ -26053,18 +27724,30 @@
         <v>97</v>
       </c>
       <c r="AH20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AI20">
         <v>0.30182073008522092</v>
       </c>
-    </row>
-    <row r="21" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK20">
+        <v>2022</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM20">
+        <v>0.49373059086467636</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I21" t="s">
         <v>156</v>
       </c>
       <c r="J21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K21">
         <v>9.3989496224169142E-4</v>
@@ -26076,7 +27759,7 @@
         <v>173</v>
       </c>
       <c r="O21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P21">
         <v>0.10864143100043103</v>
@@ -26088,7 +27771,7 @@
         <v>174</v>
       </c>
       <c r="T21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U21">
         <v>0.10635490966584987</v>
@@ -26103,7 +27786,7 @@
         <v>5.197026576834151E-2</v>
       </c>
       <c r="Z21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AA21" t="s">
         <v>25</v>
@@ -26112,7 +27795,7 @@
         <v>22</v>
       </c>
       <c r="AD21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AE21">
         <v>0.12346644850062671</v>
@@ -26121,18 +27804,30 @@
         <v>97</v>
       </c>
       <c r="AH21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AI21">
         <v>0.25734213655111149</v>
       </c>
-    </row>
-    <row r="22" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK21">
+        <v>2022</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM21">
+        <v>0.4171032702012783</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="9:40" x14ac:dyDescent="0.45">
       <c r="I22" t="s">
         <v>156</v>
       </c>
       <c r="J22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K22">
         <v>2.6464570429349413E-2</v>
@@ -26144,7 +27839,7 @@
         <v>173</v>
       </c>
       <c r="O22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P22">
         <v>1.3732920903749507E-2</v>
@@ -26156,7 +27851,7 @@
         <v>174</v>
       </c>
       <c r="T22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U22">
         <v>1.8793102740100733E-2</v>
@@ -26171,7 +27866,7 @@
         <v>3.5502075926708607E-2</v>
       </c>
       <c r="Z22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AA22" t="s">
         <v>25</v>
@@ -26180,7 +27875,7 @@
         <v>22</v>
       </c>
       <c r="AD22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AE22">
         <v>2.5513318273438734E-2</v>
@@ -26189,142 +27884,1586 @@
         <v>97</v>
       </c>
       <c r="AH22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AI22">
         <v>0.16641439001056568</v>
       </c>
-    </row>
-    <row r="23" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK22">
+        <v>2022</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM22">
+        <v>0.48988781912279178</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="23" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC23" t="s">
         <v>19</v>
       </c>
       <c r="AD23" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AE23">
         <v>0.11396490962699413</v>
       </c>
-    </row>
-    <row r="24" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK23">
+        <v>2025</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM23">
+        <v>0.35646666666666665</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC24" t="s">
         <v>19</v>
       </c>
       <c r="AD24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AE24">
         <v>0.11443313105699386</v>
       </c>
-    </row>
-    <row r="25" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK24">
+        <v>2025</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM24">
+        <v>0.39456666666666668</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC25" t="s">
         <v>19</v>
       </c>
       <c r="AD25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AE25">
         <v>2.0890529221147352E-2</v>
       </c>
-    </row>
-    <row r="26" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK25">
+        <v>2025</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM25">
+        <v>0.32286666666666669</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="26" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC26" t="s">
         <v>19</v>
       </c>
       <c r="AD26" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AE26">
         <v>0.11513877183469806</v>
       </c>
-    </row>
-    <row r="27" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK26">
+        <v>2025</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM26">
+        <v>0.43240000000000006</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC27" t="s">
         <v>19</v>
       </c>
       <c r="AD27" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AE27">
         <v>0.11576998456848109</v>
       </c>
-    </row>
-    <row r="28" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK27">
+        <v>2026</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM27">
+        <v>0.3231</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC28" t="s">
         <v>19</v>
       </c>
       <c r="AD28" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AE28">
         <v>2.1135955657045666E-2</v>
       </c>
-    </row>
-    <row r="29" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK28">
+        <v>2026</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM28">
+        <v>0.41533333333333333</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC29" t="s">
         <v>19</v>
       </c>
       <c r="AD29" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AE29">
         <v>0.11512712581010943</v>
       </c>
-    </row>
-    <row r="30" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK29">
+        <v>2026</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM29">
+        <v>0.30640000000000001</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC30" t="s">
         <v>19</v>
       </c>
       <c r="AD30" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AE30">
         <v>0.1157602053259036</v>
       </c>
-    </row>
-    <row r="31" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK30">
+        <v>2026</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM30">
+        <v>0.41870000000000002</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC31" t="s">
         <v>19</v>
       </c>
       <c r="AD31" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AE31">
         <v>2.1080713138626236E-2</v>
       </c>
-    </row>
-    <row r="32" spans="9:35" x14ac:dyDescent="0.45">
+      <c r="AK31">
+        <v>2027</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM31">
+        <v>0.3463</v>
+      </c>
+      <c r="AN31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="9:40" x14ac:dyDescent="0.45">
       <c r="AC32" t="s">
         <v>19</v>
       </c>
       <c r="AD32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AE32">
         <v>0.11281539764587316</v>
       </c>
-    </row>
-    <row r="33" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK32">
+        <v>2027</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM32">
+        <v>0.42839999999999995</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="33" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC33" t="s">
         <v>19</v>
       </c>
       <c r="AD33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AE33">
         <v>0.11312629688142535</v>
       </c>
-    </row>
-    <row r="34" spans="29:31" x14ac:dyDescent="0.45">
+      <c r="AK33">
+        <v>2027</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM33">
+        <v>0.33456666666666668</v>
+      </c>
+      <c r="AN33" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="34" spans="29:40" x14ac:dyDescent="0.45">
       <c r="AC34" t="s">
         <v>19</v>
       </c>
       <c r="AD34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AE34">
         <v>2.0756979232702068E-2</v>
+      </c>
+      <c r="AK34">
+        <v>2027</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM34">
+        <v>0.37906666666666666</v>
+      </c>
+      <c r="AN34" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK35">
+        <v>2028</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM35">
+        <v>0.46473333333333339</v>
+      </c>
+      <c r="AN35" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK36">
+        <v>2028</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM36">
+        <v>0.53206666666666669</v>
+      </c>
+      <c r="AN36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="37" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK37">
+        <v>2028</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM37">
+        <v>0.41336666666666666</v>
+      </c>
+      <c r="AN37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK38">
+        <v>2028</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM38">
+        <v>0.4996666666666667</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="39" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK39">
+        <v>2029</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM39">
+        <v>0.46993333333333331</v>
+      </c>
+      <c r="AN39" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="40" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK40">
+        <v>2029</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM40">
+        <v>0.53426666666666678</v>
+      </c>
+      <c r="AN40" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK41">
+        <v>2029</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM41">
+        <v>0.40726666666666667</v>
+      </c>
+      <c r="AN41" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="42" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK42">
+        <v>2029</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM42">
+        <v>0.56016666666666659</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK43">
+        <v>2030</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM43">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="AN43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK44">
+        <v>2030</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM44">
+        <v>0.55566666666666664</v>
+      </c>
+      <c r="AN44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK45">
+        <v>2030</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM45">
+        <v>0.47039999999999998</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK46">
+        <v>2030</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM46">
+        <v>0.5427333333333334</v>
+      </c>
+      <c r="AN46" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="47" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK47">
+        <v>2031</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM47">
+        <v>0.48343333333333333</v>
+      </c>
+      <c r="AN47" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="48" spans="29:40" x14ac:dyDescent="0.45">
+      <c r="AK48">
+        <v>2031</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM48">
+        <v>0.52726666666666666</v>
+      </c>
+      <c r="AN48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK49">
+        <v>2031</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM49">
+        <v>0.42169999999999996</v>
+      </c>
+      <c r="AN49" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="50" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK50">
+        <v>2031</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM50">
+        <v>0.5726</v>
+      </c>
+      <c r="AN50" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK51">
+        <v>2032</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM51">
+        <v>0.46026666666666666</v>
+      </c>
+      <c r="AN51" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK52">
+        <v>2032</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM52">
+        <v>0.5510666666666667</v>
+      </c>
+      <c r="AN52" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK53">
+        <v>2032</v>
+      </c>
+      <c r="AL53" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM53">
+        <v>0.43703333333333333</v>
+      </c>
+      <c r="AN53" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="54" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK54">
+        <v>2032</v>
+      </c>
+      <c r="AL54" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM54">
+        <v>0.5283000000000001</v>
+      </c>
+      <c r="AN54" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="55" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK55">
+        <v>2033</v>
+      </c>
+      <c r="AL55" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM55">
+        <v>0.43390000000000001</v>
+      </c>
+      <c r="AN55" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK56">
+        <v>2033</v>
+      </c>
+      <c r="AL56" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM56">
+        <v>0.55846666666666667</v>
+      </c>
+      <c r="AN56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK57">
+        <v>2033</v>
+      </c>
+      <c r="AL57" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM57">
+        <v>0.43976666666666664</v>
+      </c>
+      <c r="AN57" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK58">
+        <v>2033</v>
+      </c>
+      <c r="AL58" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM58">
+        <v>0.56270000000000009</v>
+      </c>
+      <c r="AN58" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="59" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK59">
+        <v>2034</v>
+      </c>
+      <c r="AL59" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM59">
+        <v>0.45736666666666664</v>
+      </c>
+      <c r="AN59" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="60" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK60">
+        <v>2034</v>
+      </c>
+      <c r="AL60" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM60">
+        <v>0.54183333333333328</v>
+      </c>
+      <c r="AN60" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="61" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK61">
+        <v>2034</v>
+      </c>
+      <c r="AL61" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM61">
+        <v>0.45416666666666661</v>
+      </c>
+      <c r="AN61" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK62">
+        <v>2034</v>
+      </c>
+      <c r="AL62" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM62">
+        <v>0.5514</v>
+      </c>
+      <c r="AN62" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK63">
+        <v>2035</v>
+      </c>
+      <c r="AL63" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM63">
+        <v>0.46096666666666669</v>
+      </c>
+      <c r="AN63" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="64" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK64">
+        <v>2035</v>
+      </c>
+      <c r="AL64" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM64">
+        <v>0.57316666666666671</v>
+      </c>
+      <c r="AN64" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="65" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK65">
+        <v>2035</v>
+      </c>
+      <c r="AL65" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM65">
+        <v>0.46183333333333332</v>
+      </c>
+      <c r="AN65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="66" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK66">
+        <v>2035</v>
+      </c>
+      <c r="AL66" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM66">
+        <v>0.56873333333333331</v>
+      </c>
+      <c r="AN66" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK67">
+        <v>2036</v>
+      </c>
+      <c r="AL67" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM67">
+        <v>0.41606666666666664</v>
+      </c>
+      <c r="AN67" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="68" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK68">
+        <v>2036</v>
+      </c>
+      <c r="AL68" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM68">
+        <v>0.46343333333333336</v>
+      </c>
+      <c r="AN68" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="69" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK69">
+        <v>2036</v>
+      </c>
+      <c r="AL69" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM69">
+        <v>0.37523333333333331</v>
+      </c>
+      <c r="AN69" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="70" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK70">
+        <v>2036</v>
+      </c>
+      <c r="AL70" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM70">
+        <v>0.50216666666666665</v>
+      </c>
+      <c r="AN70" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="71" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK71">
+        <v>2037</v>
+      </c>
+      <c r="AL71" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM71">
+        <v>0.4073</v>
+      </c>
+      <c r="AN71" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="72" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK72">
+        <v>2037</v>
+      </c>
+      <c r="AL72" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM72">
+        <v>0.45883333333333326</v>
+      </c>
+      <c r="AN72" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="73" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK73">
+        <v>2037</v>
+      </c>
+      <c r="AL73" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM73">
+        <v>0.36959999999999998</v>
+      </c>
+      <c r="AN73" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="74" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK74">
+        <v>2037</v>
+      </c>
+      <c r="AL74" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM74">
+        <v>0.47373333333333334</v>
+      </c>
+      <c r="AN74" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="75" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK75">
+        <v>2038</v>
+      </c>
+      <c r="AL75" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM75">
+        <v>0.40513333333333335</v>
+      </c>
+      <c r="AN75" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="76" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK76">
+        <v>2038</v>
+      </c>
+      <c r="AL76" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM76">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="AN76" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="77" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK77">
+        <v>2038</v>
+      </c>
+      <c r="AL77" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM77">
+        <v>0.38106666666666666</v>
+      </c>
+      <c r="AN77" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="78" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK78">
+        <v>2038</v>
+      </c>
+      <c r="AL78" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM78">
+        <v>0.49100000000000005</v>
+      </c>
+      <c r="AN78" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="79" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK79">
+        <v>2039</v>
+      </c>
+      <c r="AL79" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM79">
+        <v>0.39276666666666671</v>
+      </c>
+      <c r="AN79" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="80" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK80">
+        <v>2039</v>
+      </c>
+      <c r="AL80" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM80">
+        <v>0.47500000000000003</v>
+      </c>
+      <c r="AN80" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK81">
+        <v>2039</v>
+      </c>
+      <c r="AL81" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM81">
+        <v>0.35846666666666671</v>
+      </c>
+      <c r="AN81" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="82" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK82">
+        <v>2039</v>
+      </c>
+      <c r="AL82" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM82">
+        <v>0.46533333333333332</v>
+      </c>
+      <c r="AN82" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="83" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK83">
+        <v>2040</v>
+      </c>
+      <c r="AL83" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM83">
+        <v>0.40193333333333331</v>
+      </c>
+      <c r="AN83" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="84" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK84">
+        <v>2040</v>
+      </c>
+      <c r="AL84" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM84">
+        <v>0.49133333333333334</v>
+      </c>
+      <c r="AN84" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="85" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK85">
+        <v>2040</v>
+      </c>
+      <c r="AL85" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM85">
+        <v>0.37023333333333336</v>
+      </c>
+      <c r="AN85" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="86" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK86">
+        <v>2040</v>
+      </c>
+      <c r="AL86" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM86">
+        <v>0.47066666666666662</v>
+      </c>
+      <c r="AN86" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK87">
+        <v>2041</v>
+      </c>
+      <c r="AL87" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM87">
+        <v>0.39506666666666668</v>
+      </c>
+      <c r="AN87" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="88" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK88">
+        <v>2041</v>
+      </c>
+      <c r="AL88" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM88">
+        <v>0.45800000000000002</v>
+      </c>
+      <c r="AN88" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK89">
+        <v>2041</v>
+      </c>
+      <c r="AL89" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM89">
+        <v>0.39246666666666669</v>
+      </c>
+      <c r="AN89" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="90" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK90">
+        <v>2041</v>
+      </c>
+      <c r="AL90" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM90">
+        <v>0.45179999999999998</v>
+      </c>
+      <c r="AN90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="91" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK91">
+        <v>2042</v>
+      </c>
+      <c r="AL91" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM91">
+        <v>0.40386666666666665</v>
+      </c>
+      <c r="AN91" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK92">
+        <v>2042</v>
+      </c>
+      <c r="AL92" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM92">
+        <v>0.45463333333333328</v>
+      </c>
+      <c r="AN92" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="93" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK93">
+        <v>2042</v>
+      </c>
+      <c r="AL93" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM93">
+        <v>0.35263333333333335</v>
+      </c>
+      <c r="AN93" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK94">
+        <v>2042</v>
+      </c>
+      <c r="AL94" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM94">
+        <v>0.46326666666666666</v>
+      </c>
+      <c r="AN94" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="95" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK95">
+        <v>2043</v>
+      </c>
+      <c r="AL95" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM95">
+        <v>0.41106666666666669</v>
+      </c>
+      <c r="AN95" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="96" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK96">
+        <v>2043</v>
+      </c>
+      <c r="AL96" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM96">
+        <v>0.47789999999999999</v>
+      </c>
+      <c r="AN96" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="97" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK97">
+        <v>2043</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM97">
+        <v>0.36556666666666665</v>
+      </c>
+      <c r="AN97" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="98" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK98">
+        <v>2043</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM98">
+        <v>0.46706666666666669</v>
+      </c>
+      <c r="AN98" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="99" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK99">
+        <v>2044</v>
+      </c>
+      <c r="AL99" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM99">
+        <v>0.42566666666666669</v>
+      </c>
+      <c r="AN99" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="100" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK100">
+        <v>2044</v>
+      </c>
+      <c r="AL100" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM100">
+        <v>0.44023333333333331</v>
+      </c>
+      <c r="AN100" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="101" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK101">
+        <v>2044</v>
+      </c>
+      <c r="AL101" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM101">
+        <v>0.38763333333333333</v>
+      </c>
+      <c r="AN101" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="102" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK102">
+        <v>2044</v>
+      </c>
+      <c r="AL102" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM102">
+        <v>0.46239999999999998</v>
+      </c>
+      <c r="AN102" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="103" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK103">
+        <v>2045</v>
+      </c>
+      <c r="AL103" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM103">
+        <v>0.38306666666666667</v>
+      </c>
+      <c r="AN103" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="104" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK104">
+        <v>2045</v>
+      </c>
+      <c r="AL104" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM104">
+        <v>0.45156666666666667</v>
+      </c>
+      <c r="AN104" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="105" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK105">
+        <v>2045</v>
+      </c>
+      <c r="AL105" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM105">
+        <v>0.37220000000000003</v>
+      </c>
+      <c r="AN105" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="106" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK106">
+        <v>2045</v>
+      </c>
+      <c r="AL106" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM106">
+        <v>0.45766666666666667</v>
+      </c>
+      <c r="AN106" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="107" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK107">
+        <v>2046</v>
+      </c>
+      <c r="AL107" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM107">
+        <v>0.41346666666666665</v>
+      </c>
+      <c r="AN107" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="108" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK108">
+        <v>2046</v>
+      </c>
+      <c r="AL108" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM108">
+        <v>0.46810000000000002</v>
+      </c>
+      <c r="AN108" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="109" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK109">
+        <v>2046</v>
+      </c>
+      <c r="AL109" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM109">
+        <v>0.36210000000000003</v>
+      </c>
+      <c r="AN109" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="110" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK110">
+        <v>2046</v>
+      </c>
+      <c r="AL110" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM110">
+        <v>0.45026666666666665</v>
+      </c>
+      <c r="AN110" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="111" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK111">
+        <v>2047</v>
+      </c>
+      <c r="AL111" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM111">
+        <v>0.41213333333333341</v>
+      </c>
+      <c r="AN111" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK112">
+        <v>2047</v>
+      </c>
+      <c r="AL112" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM112">
+        <v>0.44593333333333329</v>
+      </c>
+      <c r="AN112" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="113" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK113">
+        <v>2047</v>
+      </c>
+      <c r="AL113" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM113">
+        <v>0.37369999999999998</v>
+      </c>
+      <c r="AN113" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="114" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK114">
+        <v>2047</v>
+      </c>
+      <c r="AL114" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM114">
+        <v>0.47443333333333332</v>
+      </c>
+      <c r="AN114" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="115" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK115">
+        <v>2048</v>
+      </c>
+      <c r="AL115" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM115">
+        <v>0.40993333333333332</v>
+      </c>
+      <c r="AN115" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="116" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK116">
+        <v>2048</v>
+      </c>
+      <c r="AL116" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM116">
+        <v>0.45839999999999997</v>
+      </c>
+      <c r="AN116" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="117" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK117">
+        <v>2048</v>
+      </c>
+      <c r="AL117" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM117">
+        <v>0.37603333333333339</v>
+      </c>
+      <c r="AN117" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="118" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK118">
+        <v>2048</v>
+      </c>
+      <c r="AL118" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM118">
+        <v>0.44503333333333334</v>
+      </c>
+      <c r="AN118" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="119" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK119">
+        <v>2049</v>
+      </c>
+      <c r="AL119" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM119">
+        <v>0.33139999999999997</v>
+      </c>
+      <c r="AN119" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="120" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK120">
+        <v>2049</v>
+      </c>
+      <c r="AL120" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM120">
+        <v>0.4054666666666667</v>
+      </c>
+      <c r="AN120" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="121" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK121">
+        <v>2049</v>
+      </c>
+      <c r="AL121" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM121">
+        <v>0.30980000000000002</v>
+      </c>
+      <c r="AN121" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="122" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK122">
+        <v>2049</v>
+      </c>
+      <c r="AL122" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM122">
+        <v>0.40246666666666669</v>
+      </c>
+      <c r="AN122" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="123" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK123">
+        <v>2050</v>
+      </c>
+      <c r="AL123" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM123">
+        <v>0.33779999999999993</v>
+      </c>
+      <c r="AN123" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="124" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK124">
+        <v>2050</v>
+      </c>
+      <c r="AL124" t="s">
+        <v>190</v>
+      </c>
+      <c r="AM124">
+        <v>0.39460000000000001</v>
+      </c>
+      <c r="AN124" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="125" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK125">
+        <v>2050</v>
+      </c>
+      <c r="AL125" t="s">
+        <v>191</v>
+      </c>
+      <c r="AM125">
+        <v>0.31446666666666667</v>
+      </c>
+      <c r="AN125" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="126" spans="37:40" x14ac:dyDescent="0.45">
+      <c r="AK126">
+        <v>2050</v>
+      </c>
+      <c r="AL126" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM126">
+        <v>0.38813333333333327</v>
+      </c>
+      <c r="AN126" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F282675D-FBC6-4504-86BD-BAF037B32056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45107E7E-A079-4A55-8189-888FF7AB2D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45107E7E-A079-4A55-8189-888FF7AB2D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D1F27B-F12D-4192-AA2D-F5E073C6107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_BRA/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2D1F27B-F12D-4192-AA2D-F5E073C6107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784CD2F5-568E-4A43-92CE-B45471D88669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
